--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -928,6 +928,1456 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123325144</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kalberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>601142</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6917955</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2024_1813</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123325150</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79384</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kalberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>601166</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6918041</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2024_1807</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2 dm2</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123325155</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56688</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kalberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>601273</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6918060</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2024_1802</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123325157</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92225</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>kalberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>601336</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6918095</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2024_1800</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123325162</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79384</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kalberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>601342</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6918020</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2024_1795</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0,5 dm2</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123325153</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kalberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>601201</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6918045</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2024_1804</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3 dm2</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123325147</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kalberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>601149</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6918014</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2024_1810</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123325160</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92225</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kalberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>601338</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6918067</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2024_1797</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123325156</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80723</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>kalberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>601273</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6918078</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2024_1801</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123325137</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58310</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kalberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>601232</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6917971</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2024_1820</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>juvenil</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123325145</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kalberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>601156</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6917982</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2024_1812</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123324911</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325144</v>
+        <v>123325147</v>
       </c>
       <c r="B4" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601142</v>
+        <v>601149</v>
       </c>
       <c r="R4" t="n">
-        <v>6917955</v>
+        <v>6918014</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1813</t>
+          <t>2024_1810</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325150</v>
+        <v>123325144</v>
       </c>
       <c r="B5" t="n">
-        <v>79384</v>
+        <v>90955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,21 +1081,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601166</v>
+        <v>601142</v>
       </c>
       <c r="R5" t="n">
-        <v>6918041</v>
+        <v>6917955</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1807</t>
+          <t>2024_1813</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,12 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:49</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2 dm2</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325155</v>
+        <v>123325160</v>
       </c>
       <c r="B6" t="n">
-        <v>56688</v>
+        <v>92228</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1212,30 +1207,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601273</v>
+        <v>601338</v>
       </c>
       <c r="R6" t="n">
-        <v>6918060</v>
+        <v>6918067</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1802</t>
+          <t>2024_1797</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>spillning</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,10 +1325,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325157</v>
+        <v>123325145</v>
       </c>
       <c r="B7" t="n">
-        <v>92225</v>
+        <v>98368</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,47 +1337,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601336</v>
+        <v>601156</v>
       </c>
       <c r="R7" t="n">
-        <v>6918095</v>
+        <v>6917982</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,7 +1404,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1800</t>
+          <t>2024_1812</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1419,7 +1414,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1429,7 +1424,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1463,7 +1458,7 @@
         <v>123325162</v>
       </c>
       <c r="B8" t="n">
-        <v>79384</v>
+        <v>79387</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1595,10 +1590,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325153</v>
+        <v>123325157</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>92228</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1611,43 +1606,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601201</v>
+        <v>601336</v>
       </c>
       <c r="R9" t="n">
-        <v>6918045</v>
+        <v>6918095</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,7 +1669,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1804</t>
+          <t>2024_1800</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1684,7 +1679,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1694,12 +1689,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>3 dm2</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1730,10 +1720,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325147</v>
+        <v>123325155</v>
       </c>
       <c r="B10" t="n">
-        <v>90952</v>
+        <v>56691</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1742,25 +1732,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1768,21 +1758,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601149</v>
+        <v>601273</v>
       </c>
       <c r="R10" t="n">
-        <v>6918014</v>
+        <v>6918060</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1809,7 +1794,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1810</t>
+          <t>2024_1802</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1819,7 +1804,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1829,7 +1814,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1860,10 +1850,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325160</v>
+        <v>123325156</v>
       </c>
       <c r="B11" t="n">
-        <v>92225</v>
+        <v>80726</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,43 +1866,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601338</v>
+        <v>601273</v>
       </c>
       <c r="R11" t="n">
-        <v>6918067</v>
+        <v>6918078</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1939,7 +1929,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1797</t>
+          <t>2024_1801</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1949,7 +1939,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1959,7 +1949,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1990,10 +1980,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325156</v>
+        <v>123325150</v>
       </c>
       <c r="B12" t="n">
-        <v>80723</v>
+        <v>79387</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2006,21 +1996,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2030,19 +2020,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601273</v>
+        <v>601166</v>
       </c>
       <c r="R12" t="n">
-        <v>6918078</v>
+        <v>6918041</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2069,7 +2059,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1801</t>
+          <t>2024_1807</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2079,7 +2069,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2089,7 +2079,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2 dm2</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2120,10 +2115,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325137</v>
+        <v>123325153</v>
       </c>
       <c r="B13" t="n">
-        <v>58310</v>
+        <v>78769</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2132,25 +2127,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>208245</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2160,7 +2155,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2169,10 +2164,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601232</v>
+        <v>601201</v>
       </c>
       <c r="R13" t="n">
-        <v>6917971</v>
+        <v>6918045</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2199,7 +2194,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1820</t>
+          <t>2024_1804</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2209,7 +2204,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2219,12 +2214,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>juvenil</t>
+          <t>3 dm2</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2255,10 +2250,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325145</v>
+        <v>123325137</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>58313</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2267,35 +2262,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2304,10 +2299,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601156</v>
+        <v>601232</v>
       </c>
       <c r="R14" t="n">
-        <v>6917982</v>
+        <v>6917971</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2334,7 +2329,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1812</t>
+          <t>2024_1820</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2344,7 +2339,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2354,7 +2349,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>juvenil</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123324911</v>
+        <v>123324912</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>5173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601137</v>
+        <v>601162</v>
       </c>
       <c r="R2" t="n">
-        <v>6918278</v>
+        <v>6918335</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_808</t>
+          <t>2024_807</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>hackspår</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324912</v>
+        <v>123324911</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,21 +843,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601162</v>
+        <v>601137</v>
       </c>
       <c r="R3" t="n">
-        <v>6918335</v>
+        <v>6918278</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_807</t>
+          <t>2024_808</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +899,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>hackspår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325147</v>
+        <v>123325156</v>
       </c>
       <c r="B4" t="n">
-        <v>90955</v>
+        <v>80728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -975,19 +975,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601149</v>
+        <v>601273</v>
       </c>
       <c r="R4" t="n">
-        <v>6918014</v>
+        <v>6918078</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1810</t>
+          <t>2024_1801</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325144</v>
+        <v>123325157</v>
       </c>
       <c r="B5" t="n">
-        <v>90955</v>
+        <v>92230</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,26 +1081,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1110,14 +1110,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601142</v>
+        <v>601336</v>
       </c>
       <c r="R5" t="n">
-        <v>6917955</v>
+        <v>6918095</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1813</t>
+          <t>2024_1800</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325160</v>
+        <v>123325153</v>
       </c>
       <c r="B6" t="n">
-        <v>92228</v>
+        <v>78771</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,31 +1211,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601338</v>
+        <v>601201</v>
       </c>
       <c r="R6" t="n">
-        <v>6918067</v>
+        <v>6918045</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1797</t>
+          <t>2024_1804</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1294,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3 dm2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1325,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325145</v>
+        <v>123325160</v>
       </c>
       <c r="B7" t="n">
-        <v>98368</v>
+        <v>92230</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1337,35 +1342,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1374,10 +1379,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601156</v>
+        <v>601338</v>
       </c>
       <c r="R7" t="n">
-        <v>6917982</v>
+        <v>6918067</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,7 +1409,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1812</t>
+          <t>2024_1797</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1414,7 +1419,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1424,7 +1429,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1455,10 +1460,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123325162</v>
+        <v>123325150</v>
       </c>
       <c r="B8" t="n">
-        <v>79387</v>
+        <v>79389</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1504,10 +1509,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601342</v>
+        <v>601166</v>
       </c>
       <c r="R8" t="n">
-        <v>6918020</v>
+        <v>6918041</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1534,7 +1539,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1795</t>
+          <t>2024_1807</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1544,7 +1549,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1554,12 +1559,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0,5 dm2</t>
+          <t>2 dm2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1590,10 +1595,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325157</v>
+        <v>123325162</v>
       </c>
       <c r="B9" t="n">
-        <v>92228</v>
+        <v>79389</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1606,43 +1611,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601336</v>
+        <v>601342</v>
       </c>
       <c r="R9" t="n">
-        <v>6918095</v>
+        <v>6918020</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1669,7 +1674,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1800</t>
+          <t>2024_1795</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1679,7 +1684,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1689,7 +1694,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0,5 dm2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1720,10 +1730,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325155</v>
+        <v>123325137</v>
       </c>
       <c r="B10" t="n">
-        <v>56691</v>
+        <v>58313</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1736,21 +1746,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>208245</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1758,16 +1768,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601273</v>
+        <v>601232</v>
       </c>
       <c r="R10" t="n">
-        <v>6918060</v>
+        <v>6917971</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1794,7 +1809,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1802</t>
+          <t>2024_1820</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1804,7 +1819,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1814,12 +1829,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>juvenil</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1850,10 +1865,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325156</v>
+        <v>123325144</v>
       </c>
       <c r="B11" t="n">
-        <v>80726</v>
+        <v>90957</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1866,21 +1881,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1890,19 +1905,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601273</v>
+        <v>601142</v>
       </c>
       <c r="R11" t="n">
-        <v>6918078</v>
+        <v>6917955</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1929,7 +1944,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1801</t>
+          <t>2024_1813</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1939,7 +1954,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1949,7 +1964,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1980,10 +1995,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325150</v>
+        <v>123325147</v>
       </c>
       <c r="B12" t="n">
-        <v>79387</v>
+        <v>90957</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1996,21 +2011,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2020,7 +2035,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2029,10 +2044,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601166</v>
+        <v>601149</v>
       </c>
       <c r="R12" t="n">
-        <v>6918041</v>
+        <v>6918014</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2059,7 +2074,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1807</t>
+          <t>2024_1810</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2069,7 +2084,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2079,12 +2094,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:49</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2 dm2</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2115,10 +2125,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325153</v>
+        <v>123325155</v>
       </c>
       <c r="B13" t="n">
-        <v>78769</v>
+        <v>56691</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2127,25 +2137,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2153,21 +2163,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601201</v>
+        <v>601273</v>
       </c>
       <c r="R13" t="n">
-        <v>6918045</v>
+        <v>6918060</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2194,7 +2199,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1804</t>
+          <t>2024_1802</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2204,7 +2209,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2214,12 +2219,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>3 dm2</t>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2250,10 +2255,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325137</v>
+        <v>123325145</v>
       </c>
       <c r="B14" t="n">
-        <v>58313</v>
+        <v>98370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2262,35 +2267,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2299,10 +2304,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601232</v>
+        <v>601156</v>
       </c>
       <c r="R14" t="n">
-        <v>6917971</v>
+        <v>6917982</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2329,7 +2334,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1820</t>
+          <t>2024_1812</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2339,7 +2344,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2349,12 +2354,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:57</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>juvenil</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325156</v>
+        <v>123325155</v>
       </c>
       <c r="B4" t="n">
-        <v>80728</v>
+        <v>56691</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,25 +947,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,21 +973,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>601273</v>
       </c>
       <c r="R4" t="n">
-        <v>6918078</v>
+        <v>6918060</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1801</t>
+          <t>2024_1802</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1029,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325157</v>
+        <v>123325156</v>
       </c>
       <c r="B5" t="n">
-        <v>92230</v>
+        <v>80729</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,31 +1081,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601336</v>
+        <v>601273</v>
       </c>
       <c r="R5" t="n">
-        <v>6918095</v>
+        <v>6918078</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1800</t>
+          <t>2024_1801</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325153</v>
+        <v>123325160</v>
       </c>
       <c r="B6" t="n">
-        <v>78771</v>
+        <v>92236</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,31 +1211,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601201</v>
+        <v>601338</v>
       </c>
       <c r="R6" t="n">
-        <v>6918045</v>
+        <v>6918067</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1804</t>
+          <t>2024_1797</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>3 dm2</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,10 +1325,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325160</v>
+        <v>123325137</v>
       </c>
       <c r="B7" t="n">
-        <v>92230</v>
+        <v>58313</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,35 +1337,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>208245</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1379,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601338</v>
+        <v>601232</v>
       </c>
       <c r="R7" t="n">
-        <v>6918067</v>
+        <v>6917971</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,7 +1404,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1797</t>
+          <t>2024_1820</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1419,7 +1414,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1429,7 +1424,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>juvenil</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1460,10 +1460,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123325150</v>
+        <v>123325147</v>
       </c>
       <c r="B8" t="n">
-        <v>79389</v>
+        <v>90963</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1476,21 +1476,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601166</v>
+        <v>601149</v>
       </c>
       <c r="R8" t="n">
-        <v>6918041</v>
+        <v>6918014</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1807</t>
+          <t>2024_1810</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1559,12 +1559,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:49</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 dm2</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1595,10 +1590,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325162</v>
+        <v>123325157</v>
       </c>
       <c r="B9" t="n">
-        <v>79389</v>
+        <v>92236</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1611,43 +1606,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601342</v>
+        <v>601336</v>
       </c>
       <c r="R9" t="n">
-        <v>6918020</v>
+        <v>6918095</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,7 +1669,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1795</t>
+          <t>2024_1800</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1684,7 +1679,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1694,12 +1689,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>0,5 dm2</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1730,10 +1720,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325137</v>
+        <v>123325150</v>
       </c>
       <c r="B10" t="n">
-        <v>58313</v>
+        <v>79390</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1742,25 +1732,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208245</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1770,7 +1760,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1779,10 +1769,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601232</v>
+        <v>601166</v>
       </c>
       <c r="R10" t="n">
-        <v>6917971</v>
+        <v>6918041</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1809,7 +1799,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1820</t>
+          <t>2024_1807</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1819,7 +1809,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1829,12 +1819,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>juvenil</t>
+          <t>2 dm2</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1865,10 +1855,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325144</v>
+        <v>123325145</v>
       </c>
       <c r="B11" t="n">
-        <v>90957</v>
+        <v>98376</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1877,35 +1867,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1914,10 +1904,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601142</v>
+        <v>601156</v>
       </c>
       <c r="R11" t="n">
-        <v>6917955</v>
+        <v>6917982</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1944,7 +1934,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1813</t>
+          <t>2024_1812</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1954,7 +1944,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1964,7 +1954,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1995,10 +1985,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325147</v>
+        <v>123325162</v>
       </c>
       <c r="B12" t="n">
-        <v>90957</v>
+        <v>79390</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2011,21 +2001,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2035,7 +2025,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2044,10 +2034,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601149</v>
+        <v>601342</v>
       </c>
       <c r="R12" t="n">
-        <v>6918014</v>
+        <v>6918020</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2074,7 +2064,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1810</t>
+          <t>2024_1795</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2084,7 +2074,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2094,7 +2084,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>0,5 dm2</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2125,10 +2120,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325155</v>
+        <v>123325153</v>
       </c>
       <c r="B13" t="n">
-        <v>56691</v>
+        <v>78772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2137,25 +2132,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2163,16 +2158,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601273</v>
+        <v>601201</v>
       </c>
       <c r="R13" t="n">
-        <v>6918060</v>
+        <v>6918045</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1802</t>
+          <t>2024_1804</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>3 dm2</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2255,10 +2255,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325145</v>
+        <v>123325144</v>
       </c>
       <c r="B14" t="n">
-        <v>98370</v>
+        <v>90963</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2267,35 +2267,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601156</v>
+        <v>601142</v>
       </c>
       <c r="R14" t="n">
-        <v>6917982</v>
+        <v>6917955</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1812</t>
+          <t>2024_1813</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325155</v>
+        <v>123325153</v>
       </c>
       <c r="B4" t="n">
-        <v>56691</v>
+        <v>78775</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,25 +947,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,16 +973,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601273</v>
+        <v>601201</v>
       </c>
       <c r="R4" t="n">
-        <v>6918060</v>
+        <v>6918045</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1802</t>
+          <t>2024_1804</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1019,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,12 +1034,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>3 dm2</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325156</v>
+        <v>123325144</v>
       </c>
       <c r="B5" t="n">
-        <v>80729</v>
+        <v>90966</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,21 +1086,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1105,19 +1110,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601273</v>
+        <v>601142</v>
       </c>
       <c r="R5" t="n">
-        <v>6918078</v>
+        <v>6917955</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1149,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1801</t>
+          <t>2024_1813</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1159,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1169,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1198,7 +1203,7 @@
         <v>123325160</v>
       </c>
       <c r="B6" t="n">
-        <v>92236</v>
+        <v>92239</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1325,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325137</v>
+        <v>123325155</v>
       </c>
       <c r="B7" t="n">
-        <v>58313</v>
+        <v>56691</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1341,21 +1346,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208245</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1363,21 +1368,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601232</v>
+        <v>601273</v>
       </c>
       <c r="R7" t="n">
-        <v>6917971</v>
+        <v>6918060</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1820</t>
+          <t>2024_1802</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>juvenil</t>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1460,10 +1460,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123325147</v>
+        <v>123325156</v>
       </c>
       <c r="B8" t="n">
-        <v>90963</v>
+        <v>80732</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1476,21 +1476,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1500,19 +1500,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601149</v>
+        <v>601273</v>
       </c>
       <c r="R8" t="n">
-        <v>6918014</v>
+        <v>6918078</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1810</t>
+          <t>2024_1801</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1590,10 +1590,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325157</v>
+        <v>123325162</v>
       </c>
       <c r="B9" t="n">
-        <v>92236</v>
+        <v>79393</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1606,43 +1606,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601336</v>
+        <v>601342</v>
       </c>
       <c r="R9" t="n">
-        <v>6918095</v>
+        <v>6918020</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1800</t>
+          <t>2024_1795</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1689,7 +1689,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0,5 dm2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1723,7 +1728,7 @@
         <v>123325150</v>
       </c>
       <c r="B10" t="n">
-        <v>79390</v>
+        <v>79393</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1855,10 +1860,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325145</v>
+        <v>123325137</v>
       </c>
       <c r="B11" t="n">
-        <v>98376</v>
+        <v>58313</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1867,35 +1872,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1904,10 +1909,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601156</v>
+        <v>601232</v>
       </c>
       <c r="R11" t="n">
-        <v>6917982</v>
+        <v>6917971</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1934,7 +1939,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1812</t>
+          <t>2024_1820</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1944,7 +1949,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1954,7 +1959,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>juvenil</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1985,10 +1995,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325162</v>
+        <v>123325147</v>
       </c>
       <c r="B12" t="n">
-        <v>79390</v>
+        <v>90966</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2001,21 +2011,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2025,7 +2035,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2034,10 +2044,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601342</v>
+        <v>601149</v>
       </c>
       <c r="R12" t="n">
-        <v>6918020</v>
+        <v>6918014</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2064,7 +2074,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1795</t>
+          <t>2024_1810</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2074,7 +2084,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2084,12 +2094,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>0,5 dm2</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2120,10 +2125,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325153</v>
+        <v>123325157</v>
       </c>
       <c r="B13" t="n">
-        <v>78772</v>
+        <v>92239</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2136,43 +2141,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601201</v>
+        <v>601336</v>
       </c>
       <c r="R13" t="n">
-        <v>6918045</v>
+        <v>6918095</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2199,7 +2204,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1804</t>
+          <t>2024_1800</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2209,7 +2214,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2219,12 +2224,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>3 dm2</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2255,10 +2255,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325144</v>
+        <v>123325145</v>
       </c>
       <c r="B14" t="n">
-        <v>90963</v>
+        <v>98379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2267,35 +2267,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601142</v>
+        <v>601156</v>
       </c>
       <c r="R14" t="n">
-        <v>6917955</v>
+        <v>6917982</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1813</t>
+          <t>2024_1812</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123324912</v>
+        <v>123324911</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>57503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,21 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601162</v>
+        <v>601137</v>
       </c>
       <c r="R2" t="n">
-        <v>6918335</v>
+        <v>6918278</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_807</t>
+          <t>2024_808</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>hackspår</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324911</v>
+        <v>123324912</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>5174</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,16 +843,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601137</v>
+        <v>601162</v>
       </c>
       <c r="R3" t="n">
-        <v>6918278</v>
+        <v>6918335</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_808</t>
+          <t>2024_807</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,12 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>hackspår</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325153</v>
+        <v>123325147</v>
       </c>
       <c r="B4" t="n">
-        <v>78775</v>
+        <v>90983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601201</v>
+        <v>601149</v>
       </c>
       <c r="R4" t="n">
-        <v>6918045</v>
+        <v>6918014</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1804</t>
+          <t>2024_1810</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,12 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>3 dm2</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325144</v>
+        <v>123325150</v>
       </c>
       <c r="B5" t="n">
-        <v>90966</v>
+        <v>79399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,21 +1081,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1110,7 +1105,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1119,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601142</v>
+        <v>601166</v>
       </c>
       <c r="R5" t="n">
-        <v>6917955</v>
+        <v>6918041</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1813</t>
+          <t>2024_1807</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1159,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1169,7 +1164,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2 dm2</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325160</v>
+        <v>123325144</v>
       </c>
       <c r="B6" t="n">
-        <v>92239</v>
+        <v>90983</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1216,26 +1216,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601338</v>
+        <v>601142</v>
       </c>
       <c r="R6" t="n">
-        <v>6918067</v>
+        <v>6917955</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1797</t>
+          <t>2024_1813</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1333,7 +1333,7 @@
         <v>123325155</v>
       </c>
       <c r="B7" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>123325156</v>
       </c>
       <c r="B8" t="n">
-        <v>80732</v>
+        <v>80734</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325162</v>
+        <v>123325145</v>
       </c>
       <c r="B9" t="n">
-        <v>79393</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1602,35 +1602,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601342</v>
+        <v>601156</v>
       </c>
       <c r="R9" t="n">
-        <v>6918020</v>
+        <v>6917982</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1795</t>
+          <t>2024_1812</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1689,12 +1689,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>0,5 dm2</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1725,10 +1720,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325150</v>
+        <v>123325153</v>
       </c>
       <c r="B10" t="n">
-        <v>79393</v>
+        <v>78781</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1741,21 +1736,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1774,10 +1769,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601166</v>
+        <v>601201</v>
       </c>
       <c r="R10" t="n">
-        <v>6918041</v>
+        <v>6918045</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1804,7 +1799,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1807</t>
+          <t>2024_1804</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1814,7 +1809,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1824,12 +1819,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2 dm2</t>
+          <t>3 dm2</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1860,10 +1855,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325137</v>
+        <v>123325157</v>
       </c>
       <c r="B11" t="n">
-        <v>58313</v>
+        <v>92256</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,47 +1867,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208245</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601232</v>
+        <v>601336</v>
       </c>
       <c r="R11" t="n">
-        <v>6917971</v>
+        <v>6918095</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1939,7 +1934,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1820</t>
+          <t>2024_1800</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1949,7 +1944,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1959,12 +1954,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:57</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>juvenil</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1995,10 +1985,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325147</v>
+        <v>123325137</v>
       </c>
       <c r="B12" t="n">
-        <v>90966</v>
+        <v>58319</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2007,25 +1997,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>208245</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2035,7 +2025,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2044,10 +2034,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601149</v>
+        <v>601232</v>
       </c>
       <c r="R12" t="n">
-        <v>6918014</v>
+        <v>6917971</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2074,7 +2064,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1810</t>
+          <t>2024_1820</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2084,7 +2074,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2094,7 +2084,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>juvenil</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2125,10 +2120,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325157</v>
+        <v>123325162</v>
       </c>
       <c r="B13" t="n">
-        <v>92239</v>
+        <v>79399</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2141,43 +2136,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601336</v>
+        <v>601342</v>
       </c>
       <c r="R13" t="n">
-        <v>6918095</v>
+        <v>6918020</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2204,7 +2199,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1800</t>
+          <t>2024_1795</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2214,7 +2209,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2224,7 +2219,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>0,5 dm2</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2255,10 +2255,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325145</v>
+        <v>123325160</v>
       </c>
       <c r="B14" t="n">
-        <v>98379</v>
+        <v>92256</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2267,35 +2267,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601156</v>
+        <v>601338</v>
       </c>
       <c r="R14" t="n">
-        <v>6917982</v>
+        <v>6918067</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1812</t>
+          <t>2024_1797</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123324911</v>
       </c>
       <c r="B2" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>123324912</v>
       </c>
       <c r="B3" t="n">
-        <v>5174</v>
+        <v>5176</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325147</v>
+        <v>123325156</v>
       </c>
       <c r="B4" t="n">
-        <v>90983</v>
+        <v>80739</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -975,19 +975,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601149</v>
+        <v>601273</v>
       </c>
       <c r="R4" t="n">
-        <v>6918014</v>
+        <v>6918078</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1810</t>
+          <t>2024_1801</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325150</v>
+        <v>123325162</v>
       </c>
       <c r="B5" t="n">
-        <v>79399</v>
+        <v>79404</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601166</v>
+        <v>601342</v>
       </c>
       <c r="R5" t="n">
-        <v>6918041</v>
+        <v>6918020</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1807</t>
+          <t>2024_1795</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2 dm2</t>
+          <t>0,5 dm2</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325144</v>
+        <v>123325153</v>
       </c>
       <c r="B6" t="n">
-        <v>90983</v>
+        <v>78786</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601142</v>
+        <v>601201</v>
       </c>
       <c r="R6" t="n">
-        <v>6917955</v>
+        <v>6918045</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1813</t>
+          <t>2024_1804</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1299,7 +1299,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3 dm2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325155</v>
+        <v>123325160</v>
       </c>
       <c r="B7" t="n">
-        <v>56697</v>
+        <v>92261</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,30 +1347,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1374,10 +1384,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601273</v>
+        <v>601338</v>
       </c>
       <c r="R7" t="n">
-        <v>6918060</v>
+        <v>6918067</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,7 +1414,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1802</t>
+          <t>2024_1797</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1414,7 +1424,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1424,12 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>spillning</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1460,10 +1465,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123325156</v>
+        <v>123325155</v>
       </c>
       <c r="B8" t="n">
-        <v>80734</v>
+        <v>56700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1472,25 +1477,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1498,21 +1503,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>601273</v>
       </c>
       <c r="R8" t="n">
-        <v>6918078</v>
+        <v>6918060</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1801</t>
+          <t>2024_1802</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1559,7 +1559,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1590,10 +1595,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325145</v>
+        <v>123325144</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>90988</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1602,35 +1607,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1639,10 +1644,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601156</v>
+        <v>601142</v>
       </c>
       <c r="R9" t="n">
-        <v>6917982</v>
+        <v>6917955</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1669,7 +1674,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1812</t>
+          <t>2024_1813</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1679,7 +1684,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1689,7 +1694,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1720,10 +1725,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325153</v>
+        <v>123325147</v>
       </c>
       <c r="B10" t="n">
-        <v>78781</v>
+        <v>90988</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1736,21 +1741,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1760,7 +1765,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1769,10 +1774,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601201</v>
+        <v>601149</v>
       </c>
       <c r="R10" t="n">
-        <v>6918045</v>
+        <v>6918014</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1799,7 +1804,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1804</t>
+          <t>2024_1810</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1809,7 +1814,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1819,12 +1824,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>3 dm2</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1855,10 +1855,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325157</v>
+        <v>123325145</v>
       </c>
       <c r="B11" t="n">
-        <v>92256</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1867,47 +1867,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601336</v>
+        <v>601156</v>
       </c>
       <c r="R11" t="n">
-        <v>6918095</v>
+        <v>6917982</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1800</t>
+          <t>2024_1812</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1985,10 +1985,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325137</v>
+        <v>123325150</v>
       </c>
       <c r="B12" t="n">
-        <v>58319</v>
+        <v>79404</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1997,25 +1997,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208245</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601232</v>
+        <v>601166</v>
       </c>
       <c r="R12" t="n">
-        <v>6917971</v>
+        <v>6918041</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1820</t>
+          <t>2024_1807</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>juvenil</t>
+          <t>2 dm2</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2120,10 +2120,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325162</v>
+        <v>123325157</v>
       </c>
       <c r="B13" t="n">
-        <v>79399</v>
+        <v>92261</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2136,43 +2136,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601342</v>
+        <v>601336</v>
       </c>
       <c r="R13" t="n">
-        <v>6918020</v>
+        <v>6918095</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1795</t>
+          <t>2024_1800</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2219,12 +2219,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>0,5 dm2</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2255,10 +2250,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325160</v>
+        <v>123325137</v>
       </c>
       <c r="B14" t="n">
-        <v>92256</v>
+        <v>58322</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2267,35 +2262,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>208245</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2304,10 +2299,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601338</v>
+        <v>601232</v>
       </c>
       <c r="R14" t="n">
-        <v>6918067</v>
+        <v>6917971</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2334,7 +2329,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1797</t>
+          <t>2024_1820</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2344,7 +2339,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2354,7 +2349,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>juvenil</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123324911</v>
       </c>
       <c r="B2" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325156</v>
+        <v>123325144</v>
       </c>
       <c r="B4" t="n">
-        <v>80739</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -975,19 +975,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601273</v>
+        <v>601142</v>
       </c>
       <c r="R4" t="n">
-        <v>6918078</v>
+        <v>6917955</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1801</t>
+          <t>2024_1813</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325162</v>
+        <v>123325145</v>
       </c>
       <c r="B5" t="n">
-        <v>79404</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,35 +1077,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601342</v>
+        <v>601156</v>
       </c>
       <c r="R5" t="n">
-        <v>6918020</v>
+        <v>6917982</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1795</t>
+          <t>2024_1812</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,12 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>0,5 dm2</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325153</v>
+        <v>123325147</v>
       </c>
       <c r="B6" t="n">
-        <v>78786</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1216,21 +1211,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1240,7 +1235,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1249,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601201</v>
+        <v>601149</v>
       </c>
       <c r="R6" t="n">
-        <v>6918045</v>
+        <v>6918014</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1804</t>
+          <t>2024_1810</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1289,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1299,12 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>3 dm2</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1335,10 +1325,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325160</v>
+        <v>123325157</v>
       </c>
       <c r="B7" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1370,7 +1360,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1380,14 +1370,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601338</v>
+        <v>601336</v>
       </c>
       <c r="R7" t="n">
-        <v>6918067</v>
+        <v>6918095</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1414,7 +1404,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1797</t>
+          <t>2024_1800</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1424,7 +1414,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1434,7 +1424,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1465,10 +1455,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123325155</v>
+        <v>123325150</v>
       </c>
       <c r="B8" t="n">
-        <v>56700</v>
+        <v>79406</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1477,25 +1467,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1503,16 +1493,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601273</v>
+        <v>601166</v>
       </c>
       <c r="R8" t="n">
-        <v>6918060</v>
+        <v>6918041</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1539,7 +1534,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1802</t>
+          <t>2024_1807</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1549,7 +1544,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1559,12 +1554,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>2 dm2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1595,10 +1590,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325144</v>
+        <v>123325156</v>
       </c>
       <c r="B9" t="n">
-        <v>90988</v>
+        <v>80741</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1611,21 +1606,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1635,19 +1630,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601142</v>
+        <v>601273</v>
       </c>
       <c r="R9" t="n">
-        <v>6917955</v>
+        <v>6918078</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,7 +1669,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1813</t>
+          <t>2024_1801</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1684,7 +1679,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1694,7 +1689,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1725,10 +1720,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325147</v>
+        <v>123325155</v>
       </c>
       <c r="B10" t="n">
-        <v>90988</v>
+        <v>56700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1737,25 +1732,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1763,21 +1758,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601149</v>
+        <v>601273</v>
       </c>
       <c r="R10" t="n">
-        <v>6918014</v>
+        <v>6918060</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1804,7 +1794,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1810</t>
+          <t>2024_1802</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1814,7 +1804,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1824,7 +1814,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1855,10 +1850,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325145</v>
+        <v>123325162</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>79406</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1867,35 +1862,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1904,10 +1899,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601156</v>
+        <v>601342</v>
       </c>
       <c r="R11" t="n">
-        <v>6917982</v>
+        <v>6918020</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1934,7 +1929,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1812</t>
+          <t>2024_1795</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1944,7 +1939,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1954,7 +1949,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>0,5 dm2</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1985,10 +1985,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325150</v>
+        <v>123325137</v>
       </c>
       <c r="B12" t="n">
-        <v>79404</v>
+        <v>58323</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1997,25 +1997,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>208245</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601166</v>
+        <v>601232</v>
       </c>
       <c r="R12" t="n">
-        <v>6918041</v>
+        <v>6917971</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1807</t>
+          <t>2024_1820</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2 dm2</t>
+          <t>juvenil</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2120,10 +2120,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325157</v>
+        <v>123325160</v>
       </c>
       <c r="B13" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2165,14 +2165,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601336</v>
+        <v>601338</v>
       </c>
       <c r="R13" t="n">
-        <v>6918095</v>
+        <v>6918067</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1800</t>
+          <t>2024_1797</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2250,10 +2250,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325137</v>
+        <v>123325153</v>
       </c>
       <c r="B14" t="n">
-        <v>58322</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2262,25 +2262,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208245</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601232</v>
+        <v>601201</v>
       </c>
       <c r="R14" t="n">
-        <v>6917971</v>
+        <v>6918045</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1820</t>
+          <t>2024_1804</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>juvenil</t>
+          <t>3 dm2</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -1850,10 +1850,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325162</v>
+        <v>123325137</v>
       </c>
       <c r="B11" t="n">
-        <v>79406</v>
+        <v>58323</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1862,25 +1862,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>208245</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601342</v>
+        <v>601232</v>
       </c>
       <c r="R11" t="n">
-        <v>6918020</v>
+        <v>6917971</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1795</t>
+          <t>2024_1820</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0,5 dm2</t>
+          <t>juvenil</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1985,10 +1985,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325137</v>
+        <v>123325162</v>
       </c>
       <c r="B12" t="n">
-        <v>58323</v>
+        <v>79406</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1997,25 +1997,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208245</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601232</v>
+        <v>601342</v>
       </c>
       <c r="R12" t="n">
-        <v>6917971</v>
+        <v>6918020</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1820</t>
+          <t>2024_1795</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>juvenil</t>
+          <t>0,5 dm2</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325145</v>
+        <v>123325156</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>80741</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,47 +1077,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601156</v>
+        <v>601273</v>
       </c>
       <c r="R5" t="n">
-        <v>6917982</v>
+        <v>6918078</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1812</t>
+          <t>2024_1801</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325147</v>
+        <v>123325153</v>
       </c>
       <c r="B6" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601149</v>
+        <v>601201</v>
       </c>
       <c r="R6" t="n">
-        <v>6918014</v>
+        <v>6918045</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1810</t>
+          <t>2024_1804</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1294,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3 dm2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1325,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325157</v>
+        <v>123325137</v>
       </c>
       <c r="B7" t="n">
-        <v>92263</v>
+        <v>58323</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1337,47 +1342,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>208245</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601336</v>
+        <v>601232</v>
       </c>
       <c r="R7" t="n">
-        <v>6918095</v>
+        <v>6917971</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,7 +1409,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1800</t>
+          <t>2024_1820</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1414,7 +1419,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1424,7 +1429,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>juvenil</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1590,10 +1600,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325156</v>
+        <v>123325160</v>
       </c>
       <c r="B9" t="n">
-        <v>80741</v>
+        <v>92263</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1606,43 +1616,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1049</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601273</v>
+        <v>601338</v>
       </c>
       <c r="R9" t="n">
-        <v>6918078</v>
+        <v>6918067</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1669,7 +1679,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1801</t>
+          <t>2024_1797</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1679,7 +1689,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1689,7 +1699,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1720,10 +1730,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325155</v>
+        <v>123325162</v>
       </c>
       <c r="B10" t="n">
-        <v>56700</v>
+        <v>79406</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1732,25 +1742,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1758,16 +1768,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601273</v>
+        <v>601342</v>
       </c>
       <c r="R10" t="n">
-        <v>6918060</v>
+        <v>6918020</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1794,7 +1809,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1802</t>
+          <t>2024_1795</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1804,7 +1819,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1814,12 +1829,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>0,5 dm2</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1850,10 +1865,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325137</v>
+        <v>123325147</v>
       </c>
       <c r="B11" t="n">
-        <v>58323</v>
+        <v>90990</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1862,25 +1877,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208245</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1890,7 +1905,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1899,10 +1914,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601232</v>
+        <v>601149</v>
       </c>
       <c r="R11" t="n">
-        <v>6917971</v>
+        <v>6918014</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1929,7 +1944,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1820</t>
+          <t>2024_1810</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1939,7 +1954,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1949,12 +1964,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:57</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>juvenil</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1985,10 +1995,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325162</v>
+        <v>123325157</v>
       </c>
       <c r="B12" t="n">
-        <v>79406</v>
+        <v>92263</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2001,43 +2011,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601342</v>
+        <v>601336</v>
       </c>
       <c r="R12" t="n">
-        <v>6918020</v>
+        <v>6918095</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2064,7 +2074,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1795</t>
+          <t>2024_1800</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2074,7 +2084,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2084,12 +2094,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>0,5 dm2</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2120,10 +2125,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325160</v>
+        <v>123325155</v>
       </c>
       <c r="B13" t="n">
-        <v>92263</v>
+        <v>56700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2132,35 +2137,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601338</v>
+        <v>601273</v>
       </c>
       <c r="R13" t="n">
-        <v>6918067</v>
+        <v>6918060</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1797</t>
+          <t>2024_1802</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2219,7 +2219,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2250,10 +2255,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325153</v>
+        <v>123325145</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2262,35 +2267,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2299,10 +2304,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601201</v>
+        <v>601156</v>
       </c>
       <c r="R14" t="n">
-        <v>6918045</v>
+        <v>6917982</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2329,7 +2334,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1804</t>
+          <t>2024_1812</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2339,7 +2344,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2349,12 +2354,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>3 dm2</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325137</v>
+        <v>123325150</v>
       </c>
       <c r="B7" t="n">
-        <v>58323</v>
+        <v>79406</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,25 +1342,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208245</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601232</v>
+        <v>601166</v>
       </c>
       <c r="R7" t="n">
-        <v>6917971</v>
+        <v>6918041</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1820</t>
+          <t>2024_1807</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>juvenil</t>
+          <t>2 dm2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1465,10 +1465,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123325150</v>
+        <v>123325137</v>
       </c>
       <c r="B8" t="n">
-        <v>79406</v>
+        <v>58323</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1477,25 +1477,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>208245</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601166</v>
+        <v>601232</v>
       </c>
       <c r="R8" t="n">
-        <v>6918041</v>
+        <v>6917971</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1807</t>
+          <t>2024_1820</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2 dm2</t>
+          <t>juvenil</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325144</v>
+        <v>123325150</v>
       </c>
       <c r="B4" t="n">
-        <v>90990</v>
+        <v>79406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601142</v>
+        <v>601166</v>
       </c>
       <c r="R4" t="n">
-        <v>6917955</v>
+        <v>6918041</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1813</t>
+          <t>2024_1807</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1034,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2 dm2</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325156</v>
+        <v>123325137</v>
       </c>
       <c r="B5" t="n">
-        <v>80741</v>
+        <v>58323</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,25 +1082,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>208245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1105,19 +1110,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601273</v>
+        <v>601232</v>
       </c>
       <c r="R5" t="n">
-        <v>6918078</v>
+        <v>6917971</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1149,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1801</t>
+          <t>2024_1820</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1159,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1169,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>juvenil</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325153</v>
+        <v>123325160</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>92263</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,31 +1221,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1244,10 +1254,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601201</v>
+        <v>601338</v>
       </c>
       <c r="R6" t="n">
-        <v>6918045</v>
+        <v>6918067</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1284,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1804</t>
+          <t>2024_1797</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1294,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1304,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>3 dm2</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325150</v>
+        <v>123325157</v>
       </c>
       <c r="B7" t="n">
-        <v>79406</v>
+        <v>92263</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,43 +1351,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601166</v>
+        <v>601336</v>
       </c>
       <c r="R7" t="n">
-        <v>6918041</v>
+        <v>6918095</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,7 +1414,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1807</t>
+          <t>2024_1800</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1419,7 +1424,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1429,12 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:49</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 dm2</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1465,10 +1465,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123325137</v>
+        <v>123325145</v>
       </c>
       <c r="B8" t="n">
-        <v>58323</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1477,35 +1477,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601232</v>
+        <v>601156</v>
       </c>
       <c r="R8" t="n">
-        <v>6917971</v>
+        <v>6917982</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1820</t>
+          <t>2024_1812</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1564,12 +1564,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:57</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>juvenil</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1600,10 +1595,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325160</v>
+        <v>123325147</v>
       </c>
       <c r="B9" t="n">
-        <v>92263</v>
+        <v>90990</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1616,26 +1611,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1649,10 +1644,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601338</v>
+        <v>601149</v>
       </c>
       <c r="R9" t="n">
-        <v>6918067</v>
+        <v>6918014</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1679,7 +1674,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1797</t>
+          <t>2024_1810</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1689,7 +1684,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1699,7 +1694,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1865,7 +1860,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325147</v>
+        <v>123325144</v>
       </c>
       <c r="B11" t="n">
         <v>90990</v>
@@ -1914,10 +1909,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601149</v>
+        <v>601142</v>
       </c>
       <c r="R11" t="n">
-        <v>6918014</v>
+        <v>6917955</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1944,7 +1939,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1810</t>
+          <t>2024_1813</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1954,7 +1949,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1964,7 +1959,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1995,10 +1990,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325157</v>
+        <v>123325155</v>
       </c>
       <c r="B12" t="n">
-        <v>92263</v>
+        <v>56700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2007,47 +2002,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601336</v>
+        <v>601273</v>
       </c>
       <c r="R12" t="n">
-        <v>6918095</v>
+        <v>6918060</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2074,7 +2064,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1800</t>
+          <t>2024_1802</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2084,7 +2074,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2094,7 +2084,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2125,10 +2120,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325155</v>
+        <v>123325153</v>
       </c>
       <c r="B13" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2137,25 +2132,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2163,16 +2158,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601273</v>
+        <v>601201</v>
       </c>
       <c r="R13" t="n">
-        <v>6918060</v>
+        <v>6918045</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1802</t>
+          <t>2024_1804</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>3 dm2</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2255,10 +2255,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325145</v>
+        <v>123325156</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>80741</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2267,47 +2267,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601156</v>
+        <v>601273</v>
       </c>
       <c r="R14" t="n">
-        <v>6917982</v>
+        <v>6918078</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1812</t>
+          <t>2024_1801</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325150</v>
+        <v>123325157</v>
       </c>
       <c r="B4" t="n">
-        <v>79406</v>
+        <v>92263</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,43 +951,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601166</v>
+        <v>601336</v>
       </c>
       <c r="R4" t="n">
-        <v>6918041</v>
+        <v>6918095</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1807</t>
+          <t>2024_1800</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,12 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:49</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2 dm2</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325137</v>
+        <v>123325162</v>
       </c>
       <c r="B5" t="n">
-        <v>58323</v>
+        <v>79406</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1082,25 +1077,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208245</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1110,7 +1105,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1119,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601232</v>
+        <v>601342</v>
       </c>
       <c r="R5" t="n">
-        <v>6917971</v>
+        <v>6918020</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1820</t>
+          <t>2024_1795</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1159,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1169,12 +1164,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>juvenil</t>
+          <t>0,5 dm2</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325160</v>
+        <v>123325137</v>
       </c>
       <c r="B6" t="n">
-        <v>92263</v>
+        <v>58323</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,35 +1212,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>208245</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1254,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601338</v>
+        <v>601232</v>
       </c>
       <c r="R6" t="n">
-        <v>6918067</v>
+        <v>6917971</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1279,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1797</t>
+          <t>2024_1820</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1294,7 +1289,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,7 +1299,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>juvenil</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1335,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325157</v>
+        <v>123325144</v>
       </c>
       <c r="B7" t="n">
-        <v>92263</v>
+        <v>90990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1351,26 +1351,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1380,14 +1380,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601336</v>
+        <v>601142</v>
       </c>
       <c r="R7" t="n">
-        <v>6918095</v>
+        <v>6917955</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1800</t>
+          <t>2024_1813</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1465,10 +1465,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123325145</v>
+        <v>123325147</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1477,35 +1477,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601156</v>
+        <v>601149</v>
       </c>
       <c r="R8" t="n">
-        <v>6917982</v>
+        <v>6918014</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1812</t>
+          <t>2024_1810</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325147</v>
+        <v>123325153</v>
       </c>
       <c r="B9" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601149</v>
+        <v>601201</v>
       </c>
       <c r="R9" t="n">
-        <v>6918014</v>
+        <v>6918045</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1810</t>
+          <t>2024_1804</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1694,7 +1694,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3 dm2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1725,7 +1730,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325162</v>
+        <v>123325150</v>
       </c>
       <c r="B10" t="n">
         <v>79406</v>
@@ -1774,10 +1779,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601342</v>
+        <v>601166</v>
       </c>
       <c r="R10" t="n">
-        <v>6918020</v>
+        <v>6918041</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1804,7 +1809,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1795</t>
+          <t>2024_1807</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1814,7 +1819,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1824,12 +1829,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0,5 dm2</t>
+          <t>2 dm2</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1860,10 +1865,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325144</v>
+        <v>123325155</v>
       </c>
       <c r="B11" t="n">
-        <v>90990</v>
+        <v>56700</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,25 +1877,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1898,21 +1903,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601142</v>
+        <v>601273</v>
       </c>
       <c r="R11" t="n">
-        <v>6917955</v>
+        <v>6918060</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1813</t>
+          <t>2024_1802</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1959,7 +1959,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1990,10 +1995,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325155</v>
+        <v>123325160</v>
       </c>
       <c r="B12" t="n">
-        <v>56700</v>
+        <v>92263</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2002,30 +2007,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2034,10 +2044,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601273</v>
+        <v>601338</v>
       </c>
       <c r="R12" t="n">
-        <v>6918060</v>
+        <v>6918067</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2064,7 +2074,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1802</t>
+          <t>2024_1797</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2074,7 +2084,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2084,12 +2094,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>spillning</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2120,10 +2125,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325153</v>
+        <v>123325145</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2132,35 +2137,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2169,10 +2174,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601201</v>
+        <v>601156</v>
       </c>
       <c r="R13" t="n">
-        <v>6918045</v>
+        <v>6917982</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2199,7 +2204,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1804</t>
+          <t>2024_1812</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2209,7 +2214,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2219,12 +2224,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>3 dm2</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123324911</v>
+        <v>123324912</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>5176</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601137</v>
+        <v>601162</v>
       </c>
       <c r="R2" t="n">
-        <v>6918278</v>
+        <v>6918335</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_808</t>
+          <t>2024_807</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>hackspår</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324912</v>
+        <v>123324911</v>
       </c>
       <c r="B3" t="n">
-        <v>5176</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,21 +843,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601162</v>
+        <v>601137</v>
       </c>
       <c r="R3" t="n">
-        <v>6918335</v>
+        <v>6918278</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_807</t>
+          <t>2024_808</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +899,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>hackspår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325157</v>
+        <v>123325155</v>
       </c>
       <c r="B4" t="n">
-        <v>92263</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,47 +947,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601336</v>
+        <v>601273</v>
       </c>
       <c r="R4" t="n">
-        <v>6918095</v>
+        <v>6918060</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1800</t>
+          <t>2024_1802</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1029,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,7 +1065,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325162</v>
+        <v>123325150</v>
       </c>
       <c r="B5" t="n">
         <v>79406</v>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601342</v>
+        <v>601166</v>
       </c>
       <c r="R5" t="n">
-        <v>6918020</v>
+        <v>6918041</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1795</t>
+          <t>2024_1807</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0,5 dm2</t>
+          <t>2 dm2</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1335,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325144</v>
+        <v>123325145</v>
       </c>
       <c r="B7" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1347,35 +1347,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1384,10 +1384,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601142</v>
+        <v>601156</v>
       </c>
       <c r="R7" t="n">
-        <v>6917955</v>
+        <v>6917982</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1813</t>
+          <t>2024_1812</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1465,7 +1465,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123325147</v>
+        <v>123325144</v>
       </c>
       <c r="B8" t="n">
         <v>90990</v>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601149</v>
+        <v>601142</v>
       </c>
       <c r="R8" t="n">
-        <v>6918014</v>
+        <v>6917955</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1810</t>
+          <t>2024_1813</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325153</v>
+        <v>123325157</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>92263</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1611,43 +1611,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601201</v>
+        <v>601336</v>
       </c>
       <c r="R9" t="n">
-        <v>6918045</v>
+        <v>6918095</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1804</t>
+          <t>2024_1800</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1694,12 +1694,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>3 dm2</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1730,7 +1725,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325150</v>
+        <v>123325162</v>
       </c>
       <c r="B10" t="n">
         <v>79406</v>
@@ -1779,10 +1774,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601166</v>
+        <v>601342</v>
       </c>
       <c r="R10" t="n">
-        <v>6918041</v>
+        <v>6918020</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1809,7 +1804,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1807</t>
+          <t>2024_1795</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1819,7 +1814,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1829,12 +1824,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2 dm2</t>
+          <t>0,5 dm2</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1865,10 +1860,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325155</v>
+        <v>123325147</v>
       </c>
       <c r="B11" t="n">
-        <v>56700</v>
+        <v>90990</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1877,25 +1872,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1903,16 +1898,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601273</v>
+        <v>601149</v>
       </c>
       <c r="R11" t="n">
-        <v>6918060</v>
+        <v>6918014</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1802</t>
+          <t>2024_1810</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1959,12 +1959,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>spillning</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2125,10 +2120,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325145</v>
+        <v>123325156</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>80741</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2137,47 +2132,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601156</v>
+        <v>601273</v>
       </c>
       <c r="R13" t="n">
-        <v>6917982</v>
+        <v>6918078</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2204,7 +2199,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1812</t>
+          <t>2024_1801</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2214,7 +2209,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2224,7 +2219,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2255,10 +2250,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325156</v>
+        <v>123325153</v>
       </c>
       <c r="B14" t="n">
-        <v>80741</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2271,21 +2266,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2295,19 +2290,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601273</v>
+        <v>601201</v>
       </c>
       <c r="R14" t="n">
-        <v>6918078</v>
+        <v>6918045</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2334,7 +2329,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1801</t>
+          <t>2024_1804</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2344,7 +2339,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2354,7 +2349,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>3 dm2</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325155</v>
+        <v>123325150</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>79406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,25 +947,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,16 +973,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601273</v>
+        <v>601166</v>
       </c>
       <c r="R4" t="n">
-        <v>6918060</v>
+        <v>6918041</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1802</t>
+          <t>2024_1807</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1019,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,12 +1034,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>2 dm2</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325150</v>
+        <v>123325155</v>
       </c>
       <c r="B5" t="n">
-        <v>79406</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,25 +1082,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1103,21 +1108,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601166</v>
+        <v>601273</v>
       </c>
       <c r="R5" t="n">
-        <v>6918041</v>
+        <v>6918060</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1807</t>
+          <t>2024_1802</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2 dm2</t>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325150</v>
+        <v>123325153</v>
       </c>
       <c r="B4" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601166</v>
+        <v>601201</v>
       </c>
       <c r="R4" t="n">
-        <v>6918041</v>
+        <v>6918045</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1807</t>
+          <t>2024_1804</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2 dm2</t>
+          <t>3 dm2</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325155</v>
+        <v>123325137</v>
       </c>
       <c r="B5" t="n">
-        <v>56700</v>
+        <v>58323</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,21 +1086,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>208245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1108,16 +1108,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601273</v>
+        <v>601232</v>
       </c>
       <c r="R5" t="n">
-        <v>6918060</v>
+        <v>6917971</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1149,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1802</t>
+          <t>2024_1820</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1159,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,12 +1169,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>juvenil</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325137</v>
+        <v>123325156</v>
       </c>
       <c r="B6" t="n">
-        <v>58323</v>
+        <v>80741</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1212,25 +1217,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208245</v>
+        <v>1049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1240,19 +1245,19 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601232</v>
+        <v>601273</v>
       </c>
       <c r="R6" t="n">
-        <v>6917971</v>
+        <v>6918078</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,7 +1284,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1820</t>
+          <t>2024_1801</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1289,7 +1294,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1299,12 +1304,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:57</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>juvenil</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1335,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325145</v>
+        <v>123325150</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1347,35 +1347,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1384,10 +1384,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601156</v>
+        <v>601166</v>
       </c>
       <c r="R7" t="n">
-        <v>6917982</v>
+        <v>6918041</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1812</t>
+          <t>2024_1807</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1434,7 +1434,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 dm2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1465,10 +1470,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123325144</v>
+        <v>123325145</v>
       </c>
       <c r="B8" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1477,35 +1482,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1514,10 +1519,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601142</v>
+        <v>601156</v>
       </c>
       <c r="R8" t="n">
-        <v>6917955</v>
+        <v>6917982</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1544,7 +1549,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1813</t>
+          <t>2024_1812</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1554,7 +1559,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1564,7 +1569,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1595,7 +1600,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325157</v>
+        <v>123325160</v>
       </c>
       <c r="B9" t="n">
         <v>92263</v>
@@ -1630,7 +1635,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1640,14 +1645,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601336</v>
+        <v>601338</v>
       </c>
       <c r="R9" t="n">
-        <v>6918095</v>
+        <v>6918067</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,7 +1679,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1800</t>
+          <t>2024_1797</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1684,7 +1689,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1694,7 +1699,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1725,10 +1730,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325162</v>
+        <v>123325144</v>
       </c>
       <c r="B10" t="n">
-        <v>79406</v>
+        <v>90990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1741,21 +1746,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1765,7 +1770,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1774,10 +1779,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601342</v>
+        <v>601142</v>
       </c>
       <c r="R10" t="n">
-        <v>6918020</v>
+        <v>6917955</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1804,7 +1809,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1795</t>
+          <t>2024_1813</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1814,7 +1819,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1824,12 +1829,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>0,5 dm2</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1860,10 +1860,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325147</v>
+        <v>123325162</v>
       </c>
       <c r="B11" t="n">
-        <v>90990</v>
+        <v>79406</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,21 +1876,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601149</v>
+        <v>601342</v>
       </c>
       <c r="R11" t="n">
-        <v>6918014</v>
+        <v>6918020</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1810</t>
+          <t>2024_1795</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1959,7 +1959,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>0,5 dm2</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1990,10 +1995,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325160</v>
+        <v>123325147</v>
       </c>
       <c r="B12" t="n">
-        <v>92263</v>
+        <v>90990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2006,26 +2011,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2039,10 +2044,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601338</v>
+        <v>601149</v>
       </c>
       <c r="R12" t="n">
-        <v>6918067</v>
+        <v>6918014</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2069,7 +2074,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1797</t>
+          <t>2024_1810</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2079,7 +2084,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2089,7 +2094,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2120,10 +2125,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325156</v>
+        <v>123325155</v>
       </c>
       <c r="B13" t="n">
-        <v>80741</v>
+        <v>56700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2132,25 +2137,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2158,21 +2163,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
         <v>601273</v>
       </c>
       <c r="R13" t="n">
-        <v>6918078</v>
+        <v>6918060</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1801</t>
+          <t>2024_1802</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2219,7 +2219,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2250,10 +2255,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325153</v>
+        <v>123325157</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>92263</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2266,43 +2271,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601201</v>
+        <v>601336</v>
       </c>
       <c r="R14" t="n">
-        <v>6918045</v>
+        <v>6918095</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2329,7 +2334,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1804</t>
+          <t>2024_1800</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2339,7 +2344,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2349,12 +2354,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>3 dm2</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -808,12 +808,7 @@
         <v>123324911</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>123324911</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>123324911</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>123324911</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>123324911</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>123324911</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123324912</v>
+        <v>123284479</v>
       </c>
       <c r="B2" t="n">
-        <v>5176</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>392</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +708,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601162</v>
+        <v>601120</v>
       </c>
       <c r="R2" t="n">
-        <v>6918335</v>
+        <v>6917931</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,27 +749,32 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_807</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1 dm2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Isaksson, Måns Svensson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324911</v>
+        <v>123325156</v>
       </c>
       <c r="B3" t="n">
-        <v>57681</v>
+        <v>81312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,21 +816,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,16 +838,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601137</v>
+        <v>601273</v>
       </c>
       <c r="R3" t="n">
-        <v>6918278</v>
+        <v>6918078</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,32 +879,27 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_808</t>
+          <t>2024_1801</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>hackspår</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Isaksson, Måns Svensson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -930,15 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325153</v>
+        <v>123325144</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,21 +941,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -970,7 +965,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -979,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601201</v>
+        <v>601142</v>
       </c>
       <c r="R4" t="n">
-        <v>6918045</v>
+        <v>6917955</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1004,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1804</t>
+          <t>2024_1813</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1019,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,12 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>3 dm2</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,15 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325156</v>
+        <v>123325147</v>
       </c>
       <c r="B5" t="n">
-        <v>80741</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,21 +1066,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1105,19 +1090,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601273</v>
+        <v>601149</v>
       </c>
       <c r="R5" t="n">
-        <v>6918078</v>
+        <v>6918014</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1129,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1801</t>
+          <t>2024_1810</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1139,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1149,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,15 +1180,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325147</v>
+        <v>123325157</v>
       </c>
       <c r="B6" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,26 +1191,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1240,14 +1220,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601149</v>
+        <v>601336</v>
       </c>
       <c r="R6" t="n">
-        <v>6918014</v>
+        <v>6918095</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1254,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1810</t>
+          <t>2024_1800</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1264,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1274,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1328,12 +1308,7 @@
         <v>123325160</v>
       </c>
       <c r="B7" t="n">
-        <v>92263</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1455,37 +1430,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123325137</v>
+        <v>123325153</v>
       </c>
       <c r="B8" t="n">
-        <v>58323</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208245</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1495,7 +1465,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1504,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601232</v>
+        <v>601201</v>
       </c>
       <c r="R8" t="n">
-        <v>6917971</v>
+        <v>6918045</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1534,7 +1504,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1820</t>
+          <t>2024_1804</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1544,7 +1514,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1554,12 +1524,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>juvenil</t>
+          <t>3 dm2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1590,37 +1560,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325155</v>
+        <v>123325150</v>
       </c>
       <c r="B9" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1628,16 +1593,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601273</v>
+        <v>601166</v>
       </c>
       <c r="R9" t="n">
-        <v>6918060</v>
+        <v>6918041</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1664,7 +1634,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1802</t>
+          <t>2024_1807</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1674,7 +1644,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1684,12 +1654,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>2 dm2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1720,15 +1690,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325144</v>
+        <v>123325162</v>
       </c>
       <c r="B10" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1736,21 +1701,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1760,7 +1725,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1769,10 +1734,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601142</v>
+        <v>601342</v>
       </c>
       <c r="R10" t="n">
-        <v>6917955</v>
+        <v>6918020</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1799,7 +1764,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1813</t>
+          <t>2024_1795</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1809,7 +1774,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1819,7 +1784,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0,5 dm2</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1850,15 +1820,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325162</v>
+        <v>123325143</v>
       </c>
       <c r="B11" t="n">
-        <v>79406</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1866,21 +1831,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1895,14 +1860,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kalberget, Mpd</t>
+          <t>kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601342</v>
+        <v>601119</v>
       </c>
       <c r="R11" t="n">
-        <v>6918020</v>
+        <v>6917932</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1929,7 +1894,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1795</t>
+          <t>2024_1814</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1939,7 +1904,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1949,12 +1914,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0,5 dm2</t>
+          <t>5 dm2 också med stuplav på</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1985,47 +1950,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325145</v>
+        <v>123324911</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2034,10 +1989,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601156</v>
+        <v>601137</v>
       </c>
       <c r="R12" t="n">
-        <v>6917982</v>
+        <v>6918278</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2064,27 +2019,32 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1812</t>
+          <t>2024_808</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>hackspår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2104,7 +2064,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson, Måns Svensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2115,59 +2075,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325157</v>
+        <v>123325155</v>
       </c>
       <c r="B13" t="n">
-        <v>92263</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>kalberget, Mpd</t>
+          <t>Kalberget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601336</v>
+        <v>601273</v>
       </c>
       <c r="R13" t="n">
-        <v>6918095</v>
+        <v>6918060</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2194,7 +2144,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1800</t>
+          <t>2024_1802</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2204,7 +2154,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2214,7 +2164,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2245,37 +2200,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325150</v>
+        <v>123324912</v>
       </c>
       <c r="B14" t="n">
-        <v>79406</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2283,9 +2233,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2294,10 +2244,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601166</v>
+        <v>601162</v>
       </c>
       <c r="R14" t="n">
-        <v>6918041</v>
+        <v>6918335</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2324,32 +2274,27 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1807</t>
+          <t>2024_807</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:49</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2 dm2</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2369,10 +2314,265 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
+          <t>David Isaksson, Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123325137</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kalberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>601232</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6917971</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2024_1820</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>juvenil</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
           <t>Felix Gunnarsson</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr">
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123325145</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kalberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>601156</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6917982</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2024_1812</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 9201-2022 artfynd.xlsx
+++ b/artfynd/A 9201-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284479</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -927,6 +937,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325156</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1052,6 +1067,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325144</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1177,6 +1197,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325147</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1302,6 +1327,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325157</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1427,6 +1457,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325160</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1557,6 +1592,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325153</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1687,6 +1727,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325150</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1817,6 +1862,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325162</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1947,6 +1997,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325143</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2072,6 +2127,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324911</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2197,6 +2257,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325155</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2322,6 +2387,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324912</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2452,6 +2522,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325137</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2577,8 +2652,30 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325145</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>